--- a/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA WAREHOUSE FOUNDATION/Data Warehouse Architecture/Data_Warehouse_Architecture.xlsx
+++ b/Assessment Questions/CDE/DATA ENGINEERING ASSOCIATE/DATA WAREHOUSE FOUNDATION/Data Warehouse Architecture/Data_Warehouse_Architecture.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,17 +444,12 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Difficulty</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -486,17 +481,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -528,17 +518,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -570,17 +555,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -612,17 +592,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -654,17 +629,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -696,17 +666,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -738,17 +703,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Option C</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -780,17 +740,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -822,17 +777,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -864,17 +814,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -906,17 +851,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -948,17 +888,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -990,17 +925,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Easy</t>
         </is>
       </c>
     </row>
@@ -1032,17 +962,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>MCQ</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>MCQ</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1074,17 +999,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -1116,17 +1036,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -1158,17 +1073,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1110,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -1242,17 +1147,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Option B</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -1284,17 +1184,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Option A</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Hard</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
